--- a/data/ПКО_Проверка_Сайтов.xlsx
+++ b/data/ПКО_Проверка_Сайтов.xlsx
@@ -496,11 +496,14 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>САЙТ НЕ РАБОТАЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -529,8 +532,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -559,8 +560,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -589,8 +588,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -619,8 +616,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -649,8 +644,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -679,8 +672,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -709,8 +700,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -739,8 +728,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -769,8 +756,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -799,8 +784,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -829,8 +812,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -859,8 +840,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -889,8 +868,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -919,8 +896,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -949,8 +924,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -979,8 +952,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -999,14 +970,11 @@
           <t>ООО Коллекшн Консалт</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1035,8 +1003,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1070,7 +1036,6 @@
           <t>Облигации на Мосбирже</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1104,7 +1069,6 @@
           <t>Учредитель — банк (Т-Банк)</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1138,7 +1102,6 @@
           <t>Облигации на Мосбирже + KASE</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1172,7 +1135,6 @@
           <t>Учредитель — иностранный коллекторский холдинг</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1206,7 +1168,6 @@
           <t>Секьюритизация (MBS)</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1240,7 +1201,6 @@
           <t>Финансирование через ЗПИФ</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1275,7 +1235,11 @@
           <t>Привлечение инвесторов через сайт</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>НЕОДНОЗНАЧНО</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1309,7 +1273,6 @@
           <t>Учредитель — иностранная компания (группа Svea)</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1335,11 +1298,14 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1365,11 +1331,14 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1395,11 +1364,14 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1433,7 +1405,6 @@
           <t>Привлечение инвесторов через сайт</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1459,11 +1430,14 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1497,7 +1471,6 @@
           <t>Облигации на Мосбирже</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1531,7 +1504,6 @@
           <t>Учредитель — банк (Сбербанк)</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1565,7 +1537,6 @@
           <t>Облигации на Мосбирже</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1599,7 +1570,6 @@
           <t>Финансирование через ЗПИФ</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1625,11 +1595,14 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1655,11 +1628,14 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1685,11 +1661,14 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1723,7 +1702,6 @@
           <t>Облигации на Мосбирже</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1749,11 +1727,14 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1779,11 +1760,14 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1809,11 +1793,19 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Привлечение инвесторов через сайт</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ДА</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1842,8 +1834,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1869,11 +1859,14 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1907,7 +1900,6 @@
           <t>Облигации на Мосбирже</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1941,7 +1933,6 @@
           <t>Учредитель — финтех-группа</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1967,11 +1958,14 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1997,11 +1991,14 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -2028,11 +2025,14 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -2058,11 +2058,14 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -2088,11 +2091,14 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -2121,8 +2127,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -2156,7 +2160,6 @@
           <t>Облигации на Мосбирже</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2182,11 +2185,14 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -2214,11 +2220,14 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -2252,7 +2261,6 @@
           <t>Учредитель — иностранная компания (группа Svea)</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -2278,11 +2286,14 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -2308,11 +2319,14 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -2338,11 +2352,14 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -2368,11 +2385,14 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -2398,11 +2418,14 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2437,7 +2460,6 @@
           <t>Привлечение частных инвесторов через сайт</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2463,11 +2485,14 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2493,11 +2518,14 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2523,11 +2551,14 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2553,11 +2584,14 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2583,11 +2617,14 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2614,11 +2651,14 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2644,11 +2684,14 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2674,11 +2717,14 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2704,11 +2750,14 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2734,11 +2783,14 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2764,11 +2816,14 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2794,11 +2849,14 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2824,11 +2882,14 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2854,11 +2915,14 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2884,11 +2948,14 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2914,11 +2981,14 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2944,11 +3014,14 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2974,11 +3047,14 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -3004,11 +3080,14 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -3034,11 +3113,14 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -3064,11 +3146,14 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3094,11 +3179,14 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -3132,7 +3220,6 @@
           <t>Облигации на Мосбирже</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -3158,11 +3245,14 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3188,11 +3278,14 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -3218,11 +3311,14 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -3248,11 +3344,14 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -3279,11 +3378,14 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -3309,11 +3411,14 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -3339,11 +3444,14 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -3369,11 +3477,14 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -3407,7 +3518,6 @@
           <t>Облигации на Мосбирже</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -3433,11 +3543,14 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -3463,11 +3576,14 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -3493,11 +3609,14 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -3523,11 +3642,14 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -3553,11 +3675,14 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -3583,11 +3708,14 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -3608,16 +3736,19 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>bit07.ru</t>
+          <t>ustiva.ru</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -3643,11 +3774,14 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr"/>
-      <c r="H104" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -3673,11 +3807,14 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -3704,11 +3841,14 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -3734,11 +3874,14 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -3764,11 +3907,14 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -3794,11 +3940,14 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -3824,11 +3973,14 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -3854,11 +4006,14 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -3885,11 +4040,14 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -3915,11 +4073,14 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -3945,11 +4106,14 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -3978,8 +4142,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -4005,11 +4167,14 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -4035,11 +4200,14 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -4065,11 +4233,14 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -4095,11 +4266,14 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -4125,11 +4299,14 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr"/>
-      <c r="H120" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -4148,14 +4325,11 @@
           <t>ООО ПКО Айва</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
       <c r="F121" t="inlineStr">
         <is>
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr"/>
-      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -4184,8 +4358,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr"/>
-      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -4214,8 +4386,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -4244,8 +4414,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -4274,8 +4442,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr"/>
-      <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -4304,8 +4470,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -4334,8 +4498,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -4354,14 +4516,11 @@
           <t>ООО ПКО Современная коллекторская компания</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -4390,8 +4549,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr"/>
-      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -4420,8 +4577,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -4450,8 +4605,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -4480,8 +4633,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -4510,8 +4661,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -4540,8 +4689,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr"/>
-      <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -4570,8 +4717,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -4600,8 +4745,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -4630,8 +4773,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr"/>
-      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -4660,8 +4801,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -4690,8 +4829,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -4720,8 +4857,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr"/>
-      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -4750,8 +4885,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr"/>
-      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -4781,8 +4914,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr"/>
-      <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -4811,8 +4942,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -4841,8 +4970,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -4871,8 +4998,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr"/>
-      <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -4901,8 +5026,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr"/>
-      <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -4931,8 +5054,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -4961,8 +5082,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -4991,8 +5110,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr"/>
-      <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -5021,8 +5138,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr"/>
-      <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -5051,8 +5166,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr"/>
-      <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -5081,8 +5194,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -5111,8 +5222,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr"/>
-      <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -5141,8 +5250,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -5171,8 +5278,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr"/>
-      <c r="H155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -5201,8 +5306,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -5231,8 +5334,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr"/>
-      <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -5261,8 +5362,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr"/>
-      <c r="H158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -5291,8 +5390,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr"/>
-      <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -5321,8 +5418,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -5351,8 +5446,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr"/>
-      <c r="H161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -5381,8 +5474,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr"/>
-      <c r="H162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -5411,8 +5502,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr"/>
-      <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -5441,8 +5530,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -5471,8 +5558,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr"/>
-      <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -5501,8 +5586,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr"/>
-      <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -5531,8 +5614,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr"/>
-      <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -5561,8 +5642,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -5591,8 +5670,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr"/>
-      <c r="H169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -5621,8 +5698,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr"/>
-      <c r="H170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -5651,8 +5726,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -5681,8 +5754,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr"/>
-      <c r="H172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -5716,7 +5787,6 @@
           <t>Учредитель — контакт-центр/коллекторский холдинг (эмитент облигаций)</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -5745,8 +5815,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -5775,8 +5843,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr"/>
-      <c r="H175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -5805,8 +5871,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr"/>
-      <c r="H176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -5835,8 +5899,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -5865,8 +5927,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -5895,8 +5955,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr"/>
-      <c r="H179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -5925,8 +5983,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -5955,8 +6011,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -5985,8 +6039,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr"/>
-      <c r="H182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -6015,8 +6067,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr"/>
-      <c r="H183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -6045,8 +6095,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr"/>
-      <c r="H184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -6075,8 +6123,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -6105,8 +6151,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -6135,8 +6179,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -6167,8 +6209,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -6197,8 +6237,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr"/>
-      <c r="H189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -6227,8 +6265,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr"/>
-      <c r="H190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -6257,8 +6293,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr"/>
-      <c r="H191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -6287,8 +6321,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr"/>
-      <c r="H192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -6317,8 +6349,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -6347,8 +6377,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr"/>
-      <c r="H194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -6377,8 +6405,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr"/>
-      <c r="H195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -6407,8 +6433,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -6437,8 +6461,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr"/>
-      <c r="H197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -6467,8 +6489,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr"/>
-      <c r="H198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -6497,8 +6517,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr"/>
-      <c r="H199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -6527,8 +6545,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -6558,8 +6574,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -6588,8 +6602,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr"/>
-      <c r="H202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -6618,8 +6630,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -6648,8 +6658,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr"/>
-      <c r="H204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -6678,8 +6686,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr"/>
-      <c r="H205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -6708,8 +6714,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr"/>
-      <c r="H206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -6738,8 +6742,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr"/>
-      <c r="H207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -6768,8 +6770,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -6799,8 +6799,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr"/>
-      <c r="H209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -6829,8 +6827,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr"/>
-      <c r="H210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -6859,8 +6855,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr"/>
-      <c r="H211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -6889,8 +6883,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr"/>
-      <c r="H212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -6919,8 +6911,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr"/>
-      <c r="H213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -6949,8 +6939,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr"/>
-      <c r="H214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -6979,8 +6967,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr"/>
-      <c r="H215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -7009,8 +6995,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr"/>
-      <c r="H216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -7039,8 +7023,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr"/>
-      <c r="H217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -7069,8 +7051,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr"/>
-      <c r="H218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -7099,8 +7079,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr"/>
-      <c r="H219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -7129,8 +7107,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr"/>
-      <c r="H220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -7159,8 +7135,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr"/>
-      <c r="H221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -7189,8 +7163,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr"/>
-      <c r="H222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -7219,8 +7191,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr"/>
-      <c r="H223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -7249,8 +7219,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr"/>
-      <c r="H224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -7279,8 +7247,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr"/>
-      <c r="H225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -7314,7 +7280,6 @@
           <t>Финансирование от финтех-группы + облигации</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -7343,8 +7308,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr"/>
-      <c r="H227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -7373,8 +7336,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr"/>
-      <c r="H228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -7403,8 +7364,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr"/>
-      <c r="H229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -7433,8 +7392,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr"/>
-      <c r="H230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -7463,8 +7420,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr"/>
-      <c r="H231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -7493,8 +7448,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr"/>
-      <c r="H232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -7523,8 +7476,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr"/>
-      <c r="H233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -7553,8 +7504,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr"/>
-      <c r="H234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -7583,8 +7532,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr"/>
-      <c r="H235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -7613,8 +7560,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr"/>
-      <c r="H236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -7643,8 +7588,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr"/>
-      <c r="H237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -7673,8 +7616,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr"/>
-      <c r="H238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -7703,8 +7644,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr"/>
-      <c r="H239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -7734,8 +7673,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr"/>
-      <c r="H240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -7764,8 +7701,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr"/>
-      <c r="H241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -7794,8 +7729,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -7824,8 +7757,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr"/>
-      <c r="H243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -7854,8 +7785,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr"/>
-      <c r="H244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -7884,8 +7813,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr"/>
-      <c r="H245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -7914,8 +7841,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr"/>
-      <c r="H246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -7944,8 +7869,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr"/>
-      <c r="H247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -7974,8 +7897,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr"/>
-      <c r="H248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -8004,8 +7925,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr"/>
-      <c r="H249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -8034,8 +7953,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr"/>
-      <c r="H250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -8064,8 +7981,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr"/>
-      <c r="H251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -8094,8 +8009,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr"/>
-      <c r="H252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -8124,8 +8037,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr"/>
-      <c r="H253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -8154,8 +8065,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr"/>
-      <c r="H254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -8184,8 +8093,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr"/>
-      <c r="H255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -8214,8 +8121,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr"/>
-      <c r="H256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -8234,14 +8139,11 @@
           <t>ООО ПКО Аргумент</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr"/>
       <c r="F257" t="inlineStr">
         <is>
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -8270,8 +8172,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr"/>
-      <c r="H258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -8300,8 +8200,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr"/>
-      <c r="H259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -8330,8 +8228,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr"/>
-      <c r="H260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -8360,8 +8256,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr"/>
-      <c r="H261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -8390,8 +8284,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr"/>
-      <c r="H262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -8420,8 +8312,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr"/>
-      <c r="H263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -8450,8 +8340,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr"/>
-      <c r="H264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -8480,8 +8368,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr"/>
-      <c r="H265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -8510,8 +8396,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr"/>
-      <c r="H266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -8540,8 +8424,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr"/>
-      <c r="H267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -8570,8 +8452,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr"/>
-      <c r="H268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -8600,8 +8480,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr"/>
-      <c r="H269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -8630,8 +8508,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr"/>
-      <c r="H270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -8660,8 +8536,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr"/>
-      <c r="H271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -8690,8 +8564,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr"/>
-      <c r="H272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -8720,8 +8592,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr"/>
-      <c r="H273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -8750,8 +8620,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr"/>
-      <c r="H274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -8781,8 +8649,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr"/>
-      <c r="H275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -8811,8 +8677,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr"/>
-      <c r="H276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -8841,8 +8705,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr"/>
-      <c r="H277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -8871,8 +8733,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr"/>
-      <c r="H278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -8901,8 +8761,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr"/>
-      <c r="H279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -8931,8 +8789,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr"/>
-      <c r="H280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -8961,8 +8817,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr"/>
-      <c r="H281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -8991,8 +8845,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr"/>
-      <c r="H282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -9021,8 +8873,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr"/>
-      <c r="H283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -9051,8 +8901,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr"/>
-      <c r="H284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -9081,8 +8929,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr"/>
-      <c r="H285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -9111,8 +8957,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr"/>
-      <c r="H286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -9141,8 +8985,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr"/>
-      <c r="H287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -9171,8 +9013,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr"/>
-      <c r="H288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -9201,8 +9041,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr"/>
-      <c r="H289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -9231,8 +9069,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr"/>
-      <c r="H290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -9261,8 +9097,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr"/>
-      <c r="H291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -9291,8 +9125,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr"/>
-      <c r="H292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -9322,8 +9154,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr"/>
-      <c r="H293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -9352,8 +9182,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr"/>
-      <c r="H294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -9382,8 +9210,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr"/>
-      <c r="H295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -9412,8 +9238,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G296" t="inlineStr"/>
-      <c r="H296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -9442,8 +9266,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G297" t="inlineStr"/>
-      <c r="H297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -9472,8 +9294,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G298" t="inlineStr"/>
-      <c r="H298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -9502,8 +9322,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr"/>
-      <c r="H299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -9532,8 +9350,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr"/>
-      <c r="H300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -9562,8 +9378,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G301" t="inlineStr"/>
-      <c r="H301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -9592,8 +9406,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G302" t="inlineStr"/>
-      <c r="H302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -9622,8 +9434,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G303" t="inlineStr"/>
-      <c r="H303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -9652,8 +9462,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G304" t="inlineStr"/>
-      <c r="H304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -9682,8 +9490,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G305" t="inlineStr"/>
-      <c r="H305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -9712,8 +9518,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G306" t="inlineStr"/>
-      <c r="H306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -9742,8 +9546,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr"/>
-      <c r="H307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -9772,8 +9574,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G308" t="inlineStr"/>
-      <c r="H308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -9802,8 +9602,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G309" t="inlineStr"/>
-      <c r="H309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -9832,8 +9630,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr"/>
-      <c r="H310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -9862,8 +9658,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr"/>
-      <c r="H311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -9892,8 +9686,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr"/>
-      <c r="H312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -9922,8 +9714,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G313" t="inlineStr"/>
-      <c r="H313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -9952,8 +9742,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G314" t="inlineStr"/>
-      <c r="H314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -9982,8 +9770,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G315" t="inlineStr"/>
-      <c r="H315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -10012,8 +9798,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr"/>
-      <c r="H316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -10042,8 +9826,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr"/>
-      <c r="H317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -10072,8 +9854,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G318" t="inlineStr"/>
-      <c r="H318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -10103,8 +9883,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G319" t="inlineStr"/>
-      <c r="H319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -10133,8 +9911,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G320" t="inlineStr"/>
-      <c r="H320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -10163,8 +9939,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G321" t="inlineStr"/>
-      <c r="H321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -10193,8 +9967,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G322" t="inlineStr"/>
-      <c r="H322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -10224,8 +9996,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G323" t="inlineStr"/>
-      <c r="H323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -10254,8 +10024,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G324" t="inlineStr"/>
-      <c r="H324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -10284,8 +10052,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G325" t="inlineStr"/>
-      <c r="H325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -10314,8 +10080,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G326" t="inlineStr"/>
-      <c r="H326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -10344,8 +10108,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G327" t="inlineStr"/>
-      <c r="H327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -10374,8 +10136,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G328" t="inlineStr"/>
-      <c r="H328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -10404,8 +10164,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G329" t="inlineStr"/>
-      <c r="H329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -10434,8 +10192,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr"/>
-      <c r="H330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -10461,11 +10217,14 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Не проверено</t>
-        </is>
-      </c>
-      <c r="G331" t="inlineStr"/>
-      <c r="H331" t="inlineStr"/>
+          <t>Проверено</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>НЕТ</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -10494,8 +10253,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G332" t="inlineStr"/>
-      <c r="H332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -10524,8 +10281,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G333" t="inlineStr"/>
-      <c r="H333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -10554,8 +10309,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr"/>
-      <c r="H334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -10585,8 +10338,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G335" t="inlineStr"/>
-      <c r="H335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -10615,8 +10366,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G336" t="inlineStr"/>
-      <c r="H336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -10645,8 +10394,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G337" t="inlineStr"/>
-      <c r="H337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -10675,8 +10422,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G338" t="inlineStr"/>
-      <c r="H338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -10705,8 +10450,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G339" t="inlineStr"/>
-      <c r="H339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -10735,8 +10478,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G340" t="inlineStr"/>
-      <c r="H340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -10765,8 +10506,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G341" t="inlineStr"/>
-      <c r="H341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -10795,8 +10534,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G342" t="inlineStr"/>
-      <c r="H342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -10825,8 +10562,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G343" t="inlineStr"/>
-      <c r="H343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -10855,8 +10590,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G344" t="inlineStr"/>
-      <c r="H344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -10885,8 +10618,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G345" t="inlineStr"/>
-      <c r="H345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -10915,8 +10646,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G346" t="inlineStr"/>
-      <c r="H346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -10945,8 +10674,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G347" t="inlineStr"/>
-      <c r="H347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -10975,8 +10702,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G348" t="inlineStr"/>
-      <c r="H348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -11005,8 +10730,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G349" t="inlineStr"/>
-      <c r="H349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -11035,8 +10758,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G350" t="inlineStr"/>
-      <c r="H350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -11065,8 +10786,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G351" t="inlineStr"/>
-      <c r="H351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -11095,8 +10814,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G352" t="inlineStr"/>
-      <c r="H352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -11125,8 +10842,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G353" t="inlineStr"/>
-      <c r="H353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -11155,8 +10870,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G354" t="inlineStr"/>
-      <c r="H354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -11185,8 +10898,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G355" t="inlineStr"/>
-      <c r="H355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -11215,8 +10926,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G356" t="inlineStr"/>
-      <c r="H356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -11245,8 +10954,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G357" t="inlineStr"/>
-      <c r="H357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -11275,8 +10982,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr"/>
-      <c r="H358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -11305,8 +11010,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G359" t="inlineStr"/>
-      <c r="H359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -11335,8 +11038,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G360" t="inlineStr"/>
-      <c r="H360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -11356,14 +11057,11 @@
 Юристъ</t>
         </is>
       </c>
-      <c r="E361" t="inlineStr"/>
       <c r="F361" t="inlineStr">
         <is>
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G361" t="inlineStr"/>
-      <c r="H361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -11392,8 +11090,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G362" t="inlineStr"/>
-      <c r="H362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -11422,8 +11118,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G363" t="inlineStr"/>
-      <c r="H363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -11452,8 +11146,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G364" t="inlineStr"/>
-      <c r="H364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -11484,8 +11176,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G365" t="inlineStr"/>
-      <c r="H365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -11514,8 +11204,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G366" t="inlineStr"/>
-      <c r="H366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -11544,8 +11232,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G367" t="inlineStr"/>
-      <c r="H367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -11574,8 +11260,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G368" t="inlineStr"/>
-      <c r="H368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -11604,8 +11288,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G369" t="inlineStr"/>
-      <c r="H369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -11634,8 +11316,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G370" t="inlineStr"/>
-      <c r="H370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -11664,8 +11344,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G371" t="inlineStr"/>
-      <c r="H371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -11694,8 +11372,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G372" t="inlineStr"/>
-      <c r="H372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -11724,8 +11400,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G373" t="inlineStr"/>
-      <c r="H373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -11754,8 +11428,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G374" t="inlineStr"/>
-      <c r="H374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -11784,8 +11456,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G375" t="inlineStr"/>
-      <c r="H375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -11814,8 +11484,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G376" t="inlineStr"/>
-      <c r="H376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -11844,8 +11512,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G377" t="inlineStr"/>
-      <c r="H377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -11874,8 +11540,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G378" t="inlineStr"/>
-      <c r="H378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -11904,8 +11568,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G379" t="inlineStr"/>
-      <c r="H379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -11934,8 +11596,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G380" t="inlineStr"/>
-      <c r="H380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -11964,8 +11624,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G381" t="inlineStr"/>
-      <c r="H381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -11984,14 +11642,11 @@
           <t>ООО ПКО Технология-комфорт</t>
         </is>
       </c>
-      <c r="E382" t="inlineStr"/>
       <c r="F382" t="inlineStr">
         <is>
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G382" t="inlineStr"/>
-      <c r="H382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -12020,8 +11675,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G383" t="inlineStr"/>
-      <c r="H383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -12050,8 +11703,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G384" t="inlineStr"/>
-      <c r="H384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -12080,8 +11731,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G385" t="inlineStr"/>
-      <c r="H385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -12110,8 +11759,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G386" t="inlineStr"/>
-      <c r="H386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -12140,8 +11787,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G387" t="inlineStr"/>
-      <c r="H387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -12170,8 +11815,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G388" t="inlineStr"/>
-      <c r="H388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -12200,8 +11843,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G389" t="inlineStr"/>
-      <c r="H389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -12230,8 +11871,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G390" t="inlineStr"/>
-      <c r="H390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -12260,8 +11899,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G391" t="inlineStr"/>
-      <c r="H391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -12290,8 +11927,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G392" t="inlineStr"/>
-      <c r="H392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -12321,8 +11956,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G393" t="inlineStr"/>
-      <c r="H393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -12351,8 +11984,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G394" t="inlineStr"/>
-      <c r="H394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -12371,14 +12002,11 @@
           <t>ООО Коллекторское агентство Диалог-Финанс</t>
         </is>
       </c>
-      <c r="E395" t="inlineStr"/>
       <c r="F395" t="inlineStr">
         <is>
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G395" t="inlineStr"/>
-      <c r="H395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -12407,8 +12035,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G396" t="inlineStr"/>
-      <c r="H396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -12437,8 +12063,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G397" t="inlineStr"/>
-      <c r="H397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -12467,8 +12091,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G398" t="inlineStr"/>
-      <c r="H398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -12497,8 +12119,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G399" t="inlineStr"/>
-      <c r="H399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -12527,8 +12147,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G400" t="inlineStr"/>
-      <c r="H400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -12557,8 +12175,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G401" t="inlineStr"/>
-      <c r="H401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -12577,14 +12193,11 @@
           <t>ООО ПКО Гранд Капитал</t>
         </is>
       </c>
-      <c r="E402" t="inlineStr"/>
       <c r="F402" t="inlineStr">
         <is>
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr"/>
-      <c r="H402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -12613,8 +12226,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G403" t="inlineStr"/>
-      <c r="H403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -12643,8 +12254,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G404" t="inlineStr"/>
-      <c r="H404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -12673,8 +12282,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G405" t="inlineStr"/>
-      <c r="H405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -12703,8 +12310,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G406" t="inlineStr"/>
-      <c r="H406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -12734,8 +12339,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G407" t="inlineStr"/>
-      <c r="H407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -12764,8 +12367,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G408" t="inlineStr"/>
-      <c r="H408" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -12794,8 +12395,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G409" t="inlineStr"/>
-      <c r="H409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -12824,8 +12423,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G410" t="inlineStr"/>
-      <c r="H410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -12854,8 +12451,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G411" t="inlineStr"/>
-      <c r="H411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -12884,8 +12479,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G412" t="inlineStr"/>
-      <c r="H412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -12914,8 +12507,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G413" t="inlineStr"/>
-      <c r="H413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -12944,8 +12535,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G414" t="inlineStr"/>
-      <c r="H414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -12974,8 +12563,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G415" t="inlineStr"/>
-      <c r="H415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -13004,8 +12591,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G416" t="inlineStr"/>
-      <c r="H416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -13034,8 +12619,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G417" t="inlineStr"/>
-      <c r="H417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -13064,8 +12647,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G418" t="inlineStr"/>
-      <c r="H418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -13094,8 +12675,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G419" t="inlineStr"/>
-      <c r="H419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -13124,8 +12703,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G420" t="inlineStr"/>
-      <c r="H420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -13154,8 +12731,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G421" t="inlineStr"/>
-      <c r="H421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -13184,8 +12759,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G422" t="inlineStr"/>
-      <c r="H422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -13214,8 +12787,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G423" t="inlineStr"/>
-      <c r="H423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -13244,8 +12815,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G424" t="inlineStr"/>
-      <c r="H424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -13274,8 +12843,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G425" t="inlineStr"/>
-      <c r="H425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -13304,8 +12871,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G426" t="inlineStr"/>
-      <c r="H426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -13334,8 +12899,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G427" t="inlineStr"/>
-      <c r="H427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -13364,8 +12927,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G428" t="inlineStr"/>
-      <c r="H428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -13394,8 +12955,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G429" t="inlineStr"/>
-      <c r="H429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -13424,8 +12983,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G430" t="inlineStr"/>
-      <c r="H430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -13454,8 +13011,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G431" t="inlineStr"/>
-      <c r="H431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -13484,8 +13039,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G432" t="inlineStr"/>
-      <c r="H432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -13514,8 +13067,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G433" t="inlineStr"/>
-      <c r="H433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -13544,8 +13095,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G434" t="inlineStr"/>
-      <c r="H434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -13574,8 +13123,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G435" t="inlineStr"/>
-      <c r="H435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -13604,8 +13151,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G436" t="inlineStr"/>
-      <c r="H436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -13634,8 +13179,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G437" t="inlineStr"/>
-      <c r="H437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -13664,8 +13207,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G438" t="inlineStr"/>
-      <c r="H438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -13694,8 +13235,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G439" t="inlineStr"/>
-      <c r="H439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -13724,8 +13263,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G440" t="inlineStr"/>
-      <c r="H440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -13754,8 +13291,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G441" t="inlineStr"/>
-      <c r="H441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -13785,8 +13320,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G442" t="inlineStr"/>
-      <c r="H442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -13817,8 +13350,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G443" t="inlineStr"/>
-      <c r="H443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -13847,8 +13378,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G444" t="inlineStr"/>
-      <c r="H444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -13877,8 +13406,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G445" t="inlineStr"/>
-      <c r="H445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -13907,8 +13434,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G446" t="inlineStr"/>
-      <c r="H446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -13937,8 +13462,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G447" t="inlineStr"/>
-      <c r="H447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -13967,8 +13490,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G448" t="inlineStr"/>
-      <c r="H448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -13997,8 +13518,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G449" t="inlineStr"/>
-      <c r="H449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -14027,8 +13546,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G450" t="inlineStr"/>
-      <c r="H450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -14057,8 +13574,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G451" t="inlineStr"/>
-      <c r="H451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -14087,8 +13602,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G452" t="inlineStr"/>
-      <c r="H452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -14117,8 +13630,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G453" t="inlineStr"/>
-      <c r="H453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -14147,8 +13658,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G454" t="inlineStr"/>
-      <c r="H454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -14177,8 +13686,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G455" t="inlineStr"/>
-      <c r="H455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -14207,8 +13714,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G456" t="inlineStr"/>
-      <c r="H456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -14237,8 +13742,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G457" t="inlineStr"/>
-      <c r="H457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -14268,8 +13771,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G458" t="inlineStr"/>
-      <c r="H458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -14298,8 +13799,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G459" t="inlineStr"/>
-      <c r="H459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -14328,8 +13827,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G460" t="inlineStr"/>
-      <c r="H460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -14358,8 +13855,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G461" t="inlineStr"/>
-      <c r="H461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -14388,8 +13883,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G462" t="inlineStr"/>
-      <c r="H462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -14418,8 +13911,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G463" t="inlineStr"/>
-      <c r="H463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -14448,8 +13939,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G464" t="inlineStr"/>
-      <c r="H464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -14478,8 +13967,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G465" t="inlineStr"/>
-      <c r="H465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -14508,8 +13995,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G466" t="inlineStr"/>
-      <c r="H466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -14538,8 +14023,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G467" t="inlineStr"/>
-      <c r="H467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -14568,8 +14051,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G468" t="inlineStr"/>
-      <c r="H468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -14598,8 +14079,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G469" t="inlineStr"/>
-      <c r="H469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -14628,8 +14107,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G470" t="inlineStr"/>
-      <c r="H470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -14658,8 +14135,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G471" t="inlineStr"/>
-      <c r="H471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -14688,8 +14163,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G472" t="inlineStr"/>
-      <c r="H472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -14708,14 +14181,11 @@
           <t>ООО НИКА</t>
         </is>
       </c>
-      <c r="E473" t="inlineStr"/>
       <c r="F473" t="inlineStr">
         <is>
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G473" t="inlineStr"/>
-      <c r="H473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -14744,8 +14214,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G474" t="inlineStr"/>
-      <c r="H474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -14774,8 +14242,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G475" t="inlineStr"/>
-      <c r="H475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -14804,8 +14270,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G476" t="inlineStr"/>
-      <c r="H476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -14834,8 +14298,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G477" t="inlineStr"/>
-      <c r="H477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -14864,8 +14326,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G478" t="inlineStr"/>
-      <c r="H478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -14894,8 +14354,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G479" t="inlineStr"/>
-      <c r="H479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -14924,8 +14382,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G480" t="inlineStr"/>
-      <c r="H480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -14954,8 +14410,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G481" t="inlineStr"/>
-      <c r="H481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -14984,8 +14438,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G482" t="inlineStr"/>
-      <c r="H482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -15014,8 +14466,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G483" t="inlineStr"/>
-      <c r="H483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -15044,8 +14494,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G484" t="inlineStr"/>
-      <c r="H484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -15074,8 +14522,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G485" t="inlineStr"/>
-      <c r="H485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -15104,8 +14550,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G486" t="inlineStr"/>
-      <c r="H486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -15134,8 +14578,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G487" t="inlineStr"/>
-      <c r="H487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -15164,8 +14606,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G488" t="inlineStr"/>
-      <c r="H488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -15194,8 +14634,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G489" t="inlineStr"/>
-      <c r="H489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -15224,8 +14662,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G490" t="inlineStr"/>
-      <c r="H490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -15254,8 +14690,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G491" t="inlineStr"/>
-      <c r="H491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -15284,8 +14718,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G492" t="inlineStr"/>
-      <c r="H492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -15314,8 +14746,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G493" t="inlineStr"/>
-      <c r="H493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -15334,14 +14764,11 @@
           <t>ООО Агентство правовых услуг</t>
         </is>
       </c>
-      <c r="E494" t="inlineStr"/>
       <c r="F494" t="inlineStr">
         <is>
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G494" t="inlineStr"/>
-      <c r="H494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -15370,8 +14797,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G495" t="inlineStr"/>
-      <c r="H495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -15400,8 +14825,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G496" t="inlineStr"/>
-      <c r="H496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -15430,8 +14853,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G497" t="inlineStr"/>
-      <c r="H497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -15450,14 +14871,11 @@
           <t>ООО ПКО УралДолгНадзор</t>
         </is>
       </c>
-      <c r="E498" t="inlineStr"/>
       <c r="F498" t="inlineStr">
         <is>
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G498" t="inlineStr"/>
-      <c r="H498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -15486,8 +14904,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G499" t="inlineStr"/>
-      <c r="H499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -15516,8 +14932,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G500" t="inlineStr"/>
-      <c r="H500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -15546,8 +14960,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G501" t="inlineStr"/>
-      <c r="H501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -15576,8 +14988,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G502" t="inlineStr"/>
-      <c r="H502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -15606,8 +15016,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G503" t="inlineStr"/>
-      <c r="H503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -15636,8 +15044,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G504" t="inlineStr"/>
-      <c r="H504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -15666,8 +15072,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G505" t="inlineStr"/>
-      <c r="H505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -15696,8 +15100,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G506" t="inlineStr"/>
-      <c r="H506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -15727,8 +15129,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G507" t="inlineStr"/>
-      <c r="H507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -15757,8 +15157,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G508" t="inlineStr"/>
-      <c r="H508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -15788,8 +15186,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G509" t="inlineStr"/>
-      <c r="H509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -15818,8 +15214,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G510" t="inlineStr"/>
-      <c r="H510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -15848,8 +15242,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G511" t="inlineStr"/>
-      <c r="H511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -15878,8 +15270,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G512" t="inlineStr"/>
-      <c r="H512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -15908,8 +15298,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G513" t="inlineStr"/>
-      <c r="H513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -15938,8 +15326,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G514" t="inlineStr"/>
-      <c r="H514" t="inlineStr"/>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -15958,14 +15344,11 @@
           <t>ООО Династия</t>
         </is>
       </c>
-      <c r="E515" t="inlineStr"/>
       <c r="F515" t="inlineStr">
         <is>
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G515" t="inlineStr"/>
-      <c r="H515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -15994,8 +15377,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G516" t="inlineStr"/>
-      <c r="H516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -16024,8 +15405,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G517" t="inlineStr"/>
-      <c r="H517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -16054,8 +15433,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G518" t="inlineStr"/>
-      <c r="H518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -16074,14 +15451,11 @@
           <t>ООО ПКО ХАРД</t>
         </is>
       </c>
-      <c r="E519" t="inlineStr"/>
       <c r="F519" t="inlineStr">
         <is>
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G519" t="inlineStr"/>
-      <c r="H519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -16110,8 +15484,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G520" t="inlineStr"/>
-      <c r="H520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -16140,8 +15512,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G521" t="inlineStr"/>
-      <c r="H521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -16170,8 +15540,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G522" t="inlineStr"/>
-      <c r="H522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -16200,8 +15568,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G523" t="inlineStr"/>
-      <c r="H523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -16230,8 +15596,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G524" t="inlineStr"/>
-      <c r="H524" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -16260,8 +15624,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G525" t="inlineStr"/>
-      <c r="H525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -16290,8 +15652,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G526" t="inlineStr"/>
-      <c r="H526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -16320,8 +15680,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G527" t="inlineStr"/>
-      <c r="H527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -16350,8 +15708,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G528" t="inlineStr"/>
-      <c r="H528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -16380,8 +15736,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G529" t="inlineStr"/>
-      <c r="H529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -16410,8 +15764,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G530" t="inlineStr"/>
-      <c r="H530" t="inlineStr"/>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -16440,8 +15792,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G531" t="inlineStr"/>
-      <c r="H531" t="inlineStr"/>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -16470,8 +15820,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G532" t="inlineStr"/>
-      <c r="H532" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -16500,8 +15848,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G533" t="inlineStr"/>
-      <c r="H533" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -16530,8 +15876,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G534" t="inlineStr"/>
-      <c r="H534" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -16560,8 +15904,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G535" t="inlineStr"/>
-      <c r="H535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -16590,8 +15932,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G536" t="inlineStr"/>
-      <c r="H536" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -16620,8 +15960,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G537" t="inlineStr"/>
-      <c r="H537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -16650,8 +15988,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G538" t="inlineStr"/>
-      <c r="H538" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -16680,8 +16016,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G539" t="inlineStr"/>
-      <c r="H539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -16710,8 +16044,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G540" t="inlineStr"/>
-      <c r="H540" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -16740,8 +16072,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G541" t="inlineStr"/>
-      <c r="H541" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -16770,8 +16100,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G542" t="inlineStr"/>
-      <c r="H542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -16800,8 +16128,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G543" t="inlineStr"/>
-      <c r="H543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -16830,8 +16156,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G544" t="inlineStr"/>
-      <c r="H544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -16860,8 +16184,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G545" t="inlineStr"/>
-      <c r="H545" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -16890,8 +16212,6 @@
           <t>Не проверено</t>
         </is>
       </c>
-      <c r="G546" t="inlineStr"/>
-      <c r="H546" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/ПКО_Проверка_Сайтов.xlsx
+++ b/data/ПКО_Проверка_Сайтов.xlsx
@@ -1237,7 +1237,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>НЕОДНОЗНАЧНО</t>
+          <t>ДА</t>
         </is>
       </c>
     </row>
